--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>56920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57890</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,11 +816,10 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
@@ -873,6 +872,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Hördes tydligt när andra mesar varnade.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,6 +1013,122 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130016233</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>470420</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6539228</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Varningsläte.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -1045,9 +1045,13 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sjökärret, Sjökärret, Vg</t>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Varningsläte.</t>
+          <t>Varningsläte från 2 talltitor med andra mesar.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130016233</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>129462997</v>
       </c>
       <c r="B3" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>130016233</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>57016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>56926</v>
+        <v>57016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>57042</v>
+        <v>57044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50753-2022 artfynd.xlsx
+++ b/artfynd/A 50753-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129461402</v>
       </c>
       <c r="B2" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129461517</v>
       </c>
       <c r="B4" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
